--- a/WorkBot/refactor-experimental/data/orders/Coffee Depot LLC/Coffee Depot LLC_Collegetown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Coffee Depot LLC/Coffee Depot LLC_Collegetown_20251114.xlsx
@@ -450,20 +450,14 @@
           <t>Monin - Cranberry</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -473,20 +467,14 @@
           <t>Monin - Vanilla Sugar Free</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -496,20 +484,14 @@
           <t>Monin - Caramel Sugar Free</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -519,20 +501,14 @@
           <t>Monin - Hazelnut</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -542,20 +518,14 @@
           <t>Monin - Toffee Nut</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -565,20 +535,14 @@
           <t>Monin - Lavender</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -588,20 +552,14 @@
           <t>Monin - Toasted Marshmallow</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -611,20 +569,14 @@
           <t>Monin - Peppermint</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>6.75</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>6.75</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
@@ -634,20 +586,14 @@
           <t>Monin - Cookie Butter</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -657,20 +603,14 @@
           <t>Monin - Turmeric</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -680,20 +620,14 @@
           <t>Monin - Caramel Apple Butter</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
